--- a/results/calibration/y-factors/BDI_calibration.xlsx
+++ b/results/calibration/y-factors/BDI_calibration.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="304">
   <si>
     <t>meta_y_factor</t>
   </si>
@@ -583,6 +583,9 @@
     <t>vaccine_waning_dur</t>
   </si>
   <si>
+    <t>vaccine_prop_clear_initial</t>
+  </si>
+  <si>
     <t>vaccine_prop_clear</t>
   </si>
   <si>
@@ -595,6 +598,12 @@
     <t>vaccine_infx_mult_gen</t>
   </si>
   <si>
+    <t>acute_vax_initial</t>
+  </si>
+  <si>
+    <t>acute_vax_reinfected</t>
+  </si>
+  <si>
     <t>sus_abneg_vax</t>
   </si>
   <si>
@@ -890,6 +899,9 @@
   </si>
   <si>
     <t>cc_cured</t>
+  </si>
+  <si>
+    <t>vaccine_prop_chronic_initial</t>
   </si>
   <si>
     <t>vaccine_prop_chronic</t>
@@ -1271,7 +1283,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O302"/>
+  <dimension ref="A1:O306"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -2092,10 +2104,10 @@
       </c>
       <c r="B19" s="1"/>
       <c r="C19">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E19">
         <v>0.01</v>
@@ -2137,7 +2149,7 @@
       </c>
       <c r="B20" s="1"/>
       <c r="C20">
-        <v>3.078125</v>
+        <v>3.069862651173025</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -3802,7 +3814,7 @@
       </c>
       <c r="B57" s="1"/>
       <c r="C57">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -3847,7 +3859,7 @@
       </c>
       <c r="B58" s="1"/>
       <c r="C58">
-        <v>1</v>
+        <v>2.227282349066809</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -3892,7 +3904,7 @@
       </c>
       <c r="B59" s="1"/>
       <c r="C59">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -3937,7 +3949,7 @@
       </c>
       <c r="B60" s="1"/>
       <c r="C60">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -8887,7 +8899,7 @@
       </c>
       <c r="B170" s="1"/>
       <c r="C170">
-        <v>0.1257478713989257</v>
+        <v>0.125629675388336</v>
       </c>
       <c r="D170">
         <v>1</v>
@@ -13970,9 +13982,7 @@
       <c r="A283" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B283" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="B283" s="1"/>
       <c r="C283">
         <v>1</v>
       </c>
@@ -13980,16 +13990,44 @@
         <v>1</v>
       </c>
       <c r="E283">
+        <v>1</v>
+      </c>
+      <c r="F283">
+        <v>1</v>
+      </c>
+      <c r="G283">
+        <v>1</v>
+      </c>
+      <c r="H283">
+        <v>1</v>
+      </c>
+      <c r="I283">
+        <v>1</v>
+      </c>
+      <c r="J283">
+        <v>1</v>
+      </c>
+      <c r="K283">
+        <v>1</v>
+      </c>
+      <c r="L283">
+        <v>1</v>
+      </c>
+      <c r="M283">
+        <v>1</v>
+      </c>
+      <c r="N283">
+        <v>1</v>
+      </c>
+      <c r="O283">
         <v>1</v>
       </c>
     </row>
     <row r="284" spans="1:15">
       <c r="A284" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="B284" s="1" t="s">
-        <v>2</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="B284" s="1"/>
       <c r="C284">
         <v>1</v>
       </c>
@@ -13997,31 +14035,123 @@
         <v>1</v>
       </c>
       <c r="E284">
+        <v>1</v>
+      </c>
+      <c r="F284">
+        <v>1</v>
+      </c>
+      <c r="G284">
+        <v>1</v>
+      </c>
+      <c r="H284">
+        <v>1</v>
+      </c>
+      <c r="I284">
+        <v>1</v>
+      </c>
+      <c r="J284">
+        <v>1</v>
+      </c>
+      <c r="K284">
+        <v>1</v>
+      </c>
+      <c r="L284">
+        <v>1</v>
+      </c>
+      <c r="M284">
+        <v>1</v>
+      </c>
+      <c r="N284">
+        <v>1</v>
+      </c>
+      <c r="O284">
         <v>1</v>
       </c>
     </row>
     <row r="285" spans="1:15">
       <c r="A285" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="B285" s="1" t="s">
-        <v>11</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="B285" s="1"/>
       <c r="C285">
         <v>1</v>
       </c>
+      <c r="D285">
+        <v>1</v>
+      </c>
+      <c r="E285">
+        <v>1</v>
+      </c>
+      <c r="F285">
+        <v>1</v>
+      </c>
+      <c r="G285">
+        <v>1</v>
+      </c>
+      <c r="H285">
+        <v>1</v>
+      </c>
+      <c r="I285">
+        <v>1</v>
+      </c>
+      <c r="J285">
+        <v>1</v>
+      </c>
+      <c r="K285">
+        <v>1</v>
+      </c>
+      <c r="L285">
+        <v>1</v>
+      </c>
+      <c r="M285">
+        <v>1</v>
+      </c>
       <c r="N285">
+        <v>1</v>
+      </c>
+      <c r="O285">
         <v>1</v>
       </c>
     </row>
     <row r="286" spans="1:15">
       <c r="A286" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="B286" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="B286" s="1"/>
       <c r="C286">
+        <v>1</v>
+      </c>
+      <c r="D286">
+        <v>1</v>
+      </c>
+      <c r="E286">
+        <v>1</v>
+      </c>
+      <c r="F286">
+        <v>1</v>
+      </c>
+      <c r="G286">
+        <v>1</v>
+      </c>
+      <c r="H286">
+        <v>1</v>
+      </c>
+      <c r="I286">
+        <v>1</v>
+      </c>
+      <c r="J286">
+        <v>1</v>
+      </c>
+      <c r="K286">
+        <v>1</v>
+      </c>
+      <c r="L286">
+        <v>1</v>
+      </c>
+      <c r="M286">
+        <v>1</v>
+      </c>
+      <c r="N286">
         <v>1</v>
       </c>
       <c r="O286">
@@ -14030,94 +14160,100 @@
     </row>
     <row r="287" spans="1:15">
       <c r="A287" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C287">
         <v>1</v>
       </c>
-      <c r="H287">
+      <c r="D287">
+        <v>1</v>
+      </c>
+      <c r="E287">
         <v>1</v>
       </c>
     </row>
     <row r="288" spans="1:15">
       <c r="A288" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C288">
         <v>1</v>
       </c>
-      <c r="I288">
+      <c r="D288">
+        <v>1</v>
+      </c>
+      <c r="E288">
         <v>1</v>
       </c>
     </row>
     <row r="289" spans="1:15">
       <c r="A289" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C289">
         <v>1</v>
       </c>
-      <c r="J289">
+      <c r="N289">
         <v>1</v>
       </c>
     </row>
     <row r="290" spans="1:15">
       <c r="A290" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C290">
         <v>1</v>
       </c>
-      <c r="K290">
+      <c r="O290">
         <v>1</v>
       </c>
     </row>
     <row r="291" spans="1:15">
       <c r="A291" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C291">
         <v>1</v>
       </c>
-      <c r="L291">
+      <c r="H291">
         <v>1</v>
       </c>
     </row>
     <row r="292" spans="1:15">
       <c r="A292" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C292">
         <v>1</v>
       </c>
-      <c r="M292">
+      <c r="I292">
         <v>1</v>
       </c>
     </row>
     <row r="293" spans="1:15">
       <c r="A293" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C293">
         <v>1</v>
@@ -14128,10 +14264,10 @@
     </row>
     <row r="294" spans="1:15">
       <c r="A294" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C294">
         <v>1</v>
@@ -14142,7 +14278,7 @@
     </row>
     <row r="295" spans="1:15">
       <c r="A295" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>7</v>
@@ -14150,13 +14286,13 @@
       <c r="C295">
         <v>1</v>
       </c>
-      <c r="D295">
-        <v>0.001</v>
+      <c r="L295">
+        <v>1</v>
       </c>
     </row>
     <row r="296" spans="1:15">
       <c r="A296" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B296" s="1" t="s">
         <v>8</v>
@@ -14164,13 +14300,13 @@
       <c r="C296">
         <v>1</v>
       </c>
-      <c r="E296">
-        <v>1.06943359375</v>
+      <c r="M296">
+        <v>1</v>
       </c>
     </row>
     <row r="297" spans="1:15">
       <c r="A297" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B297" s="1" t="s">
         <v>1</v>
@@ -14178,13 +14314,13 @@
       <c r="C297">
         <v>1</v>
       </c>
-      <c r="N297">
+      <c r="J297">
         <v>1</v>
       </c>
     </row>
     <row r="298" spans="1:15">
       <c r="A298" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B298" s="1" t="s">
         <v>2</v>
@@ -14192,13 +14328,13 @@
       <c r="C298">
         <v>1</v>
       </c>
-      <c r="O298">
+      <c r="K298">
         <v>1</v>
       </c>
     </row>
     <row r="299" spans="1:15">
       <c r="A299" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B299" s="1" t="s">
         <v>7</v>
@@ -14206,13 +14342,13 @@
       <c r="C299">
         <v>1</v>
       </c>
-      <c r="N299">
-        <v>1</v>
+      <c r="D299">
+        <v>0.001</v>
       </c>
     </row>
     <row r="300" spans="1:15">
       <c r="A300" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B300" s="1" t="s">
         <v>8</v>
@@ -14220,248 +14356,101 @@
       <c r="C300">
         <v>1</v>
       </c>
-      <c r="O300">
-        <v>1</v>
+      <c r="E300">
+        <v>2.2336669921875</v>
       </c>
     </row>
     <row r="301" spans="1:15">
       <c r="A301" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C301">
         <v>1</v>
       </c>
-      <c r="D301">
-        <v>1</v>
-      </c>
-      <c r="J301">
-        <v>0.8830932617187498</v>
+      <c r="N301">
+        <v>1</v>
       </c>
     </row>
     <row r="302" spans="1:15">
       <c r="A302" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B302" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C302">
+        <v>1</v>
+      </c>
+      <c r="O302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:15">
+      <c r="A303" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B303" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C303">
+        <v>1</v>
+      </c>
+      <c r="N303">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:15">
+      <c r="A304" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C304">
+        <v>1</v>
+      </c>
+      <c r="O304">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:11">
+      <c r="A305" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B305" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C305">
+        <v>1</v>
+      </c>
+      <c r="D305">
+        <v>1</v>
+      </c>
+      <c r="J305">
+        <v>0.8681907653808595</v>
+      </c>
+    </row>
+    <row r="306" spans="1:11">
+      <c r="A306" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B306" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C302">
-        <v>1</v>
-      </c>
-      <c r="E302">
-        <v>1</v>
-      </c>
-      <c r="K302">
-        <v>1.037109375</v>
+      <c r="C306">
+        <v>1</v>
+      </c>
+      <c r="E306">
+        <v>1</v>
+      </c>
+      <c r="K306">
+        <v>1.7717529296875</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010042DC9346A4EFF44B9278E035670E998A" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b6002ac4d6852791cc52372fb08f1f93">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="460e4ad2-c64b-4f67-8552-094351f252e3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d81800e77b8320248f69566da91fdce8" ns2:_="">
-    <xsd:import namespace="460e4ad2-c64b-4f67-8552-094351f252e3"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="460e4ad2-c64b-4f67-8552-094351f252e3" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="9012861f-df9c-4ac0-92bd-da4c61c7cfda" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="13" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="460e4ad2-c64b-4f67-8552-094351f252e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07658E47-FD50-4ABC-83AA-98330A4D0890}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2967BF5-3AA7-4F76-B607-E06E0F67FEB9}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64B00D79-EFF1-4E14-BF3B-6014DDEEE211}"/>
 </file>